--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_903_Balearic_Islands_Spain.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_903_Balearic_Islands_Spain.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rdc7b0516c1db4ee3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R82bf626d990d43e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R94c5fa350b0b43b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R70c9d4a0de924837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf6dd8aab338246b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R237ebc2a83e84534"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R231c015c2e734c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc4fc8e3aff91468c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4f79606d651b4627"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R859f10740c284983"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R073ce9d584c7498c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rdb2f40fac30c4c7c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ903CommercialTable" displayName="EEZ903CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ903CommercialTable" displayName="EEZ903CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ903FunctionalTable" displayName="EEZ903FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ903FunctionalTable" displayName="EEZ903FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ903ValidationTable" displayName="EEZ903ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ903ValidationTable" displayName="EEZ903ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -13223,7 +13177,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9ae02367de34518"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7a86153695c4a2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13233,20 +13187,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13254,714 +13198,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>246.7655621586</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>246.7655621586</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$188,A2,'Species'!$U$2:$U$188))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>31789.562482412057</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>31789.562482412057</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>138.8352095434</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.257280100530457</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1808.3400484958388</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>138.8352095434</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2033.0060513863612</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$188,A3,'Species'!$U$2:$U$188))</x:f>
-        <x:v>282252.8211472257</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.257280100530457</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1808.3400484958388</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>251061.26955864188</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>31191.551588583796</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.124238802916187</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.12423880291618696</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>402.72670208709997</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.218130673548974</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>165.24589267882945</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>402.72670208709997</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>184.16386171209726</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$188,A4,'Species'!$U$2:$U$188))</x:f>
-        <x:v>74167.70467093767</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.218130673548974</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>165.24589267882945</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>66548.93339198384</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>7618.771278953835</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1144837473814653</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.11448374738146525</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>26.5973268938</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.656202404613881</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>453.1087037566054</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>26.5973268938</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>487.3550725798434</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$188,A5,'Species'!$U$2:$U$188))</x:f>
-        <x:v>12962.342178757719</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.656202404613881</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>453.1087037566054</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>12051.480312240417</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>910.8618665173017</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0755809114663002</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0755809114663001</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>310.4743974603</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0996553085119953</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>125.79266224204012</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>310.4743974603</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>130.72102253468344</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$188,A6,'Species'!$U$2:$U$188))</x:f>
-        <x:v>40585.53070685014</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0996553085119953</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>125.79266224204012</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>39055.40101452444</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1530.1296923257032</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0391784401792894</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03917844017928937</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>21.371671899800003</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0841970860751813</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.139396203379674</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>21.371671899800003</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>12.181629803291878</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$188,A7,'Species'!$U$2:$U$188))</x:f>
-        <x:v>260.34179536077926</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0841970860751813</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.139396203379674</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>259.4391927203082</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.9026026404710592</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0034790527637978</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0034790527637978035</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>971.3176680596999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.671202538919295</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>469.03207039585993</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>971.3176680596999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>812.8984622402736</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$188,A8,'Species'!$U$2:$U$188))</x:f>
-        <x:v>789582.6387125386</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.671202538919295</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>469.03207039585993</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>455579.1368621197</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>334003.5018504189</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.733140468527435</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7331404685274351</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2775.6115091679003</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4756980103634727</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>299.01846681840175</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2775.6115091679003</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>571.5993814523424</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$188,A9,'Species'!$U$2:$U$188))</x:f>
-        <x:v>1586537.8217923744</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4756980103634727</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>299.01846681840175</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>829959.0979548958</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>756578.7238374786</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.9115855536757969</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.9115855536757967</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>19.2273334355</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.493733296260857</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>311.69748368718393</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>19.2273334355</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>326.6133498971817</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$188,A10,'Species'!$U$2:$U$188))</x:f>
-        <x:v>6279.903782958742</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.493733296260857</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>311.69748368718393</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5993.111449859807</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>286.79233309893516</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0478536625754964</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.04785366257549639</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>181.37635281220003</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.0564392696512055</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1138.778527600707</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>181.37635281220003</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1288.2920366876342</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$188,A11,'Species'!$U$2:$U$188))</x:f>
-        <x:v>233665.7109714041</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.0564392696512055</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1138.778527600707</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>206547.49599706352</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>27118.214974340575</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1312928769406438</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.1312928769406438</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>3577.0459599010996</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.351906159810572</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2248.568693812537</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>3577.0459599010996</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2372.9384883331522</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$188,A12,'Species'!$U$2:$U$188))</x:f>
-        <x:v>8488110.032785924</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.351906159810572</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2248.568693812537</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>8043233.561762228</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>444876.4710236965</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0553106493312159</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.05531064933121581</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>6664.636544243501</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.392863302051911</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2470.9462708702354</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>6664.636544243501</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2511.9080930339105</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$188,A13,'Species'!$U$2:$U$188))</x:f>
-        <x:v>16740954.472614802</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.392863302051911</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2470.9462708702354</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>16467958.815703971</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>272995.6569108311</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0165773827810707</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.01657738278107062</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2c6dc6f3f534b1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R412571cca1544e1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13971,20 +13451,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13992,1416 +13462,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>356.33189834180007</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8376366540597697</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>688.0763867144582</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>356.33189834180007</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>823.4077849920402</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$188,A2,'Species'!$U$2:$U$188))</x:f>
-        <x:v>293406.45913563046</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8376366540597697</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>688.0763867144582</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>245183.5650821294</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>48222.89405350105</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1966807768593615</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.19668077685936156</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>61.4015531383</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.447349223865081</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2801.232935120444</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>61.4015531383</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2802.450430847609</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$188,A3,'Species'!$U$2:$U$188))</x:f>
-        <x:v>172074.8090471412</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.447349223865081</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2801.232935120444</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>172000.05291855402</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>74.75612858717795</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0004346285208563</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.00043462852085619243</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.5978316764</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>831.7637711026708</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.5978316764</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$188,A4,'Species'!$U$2:$U$188))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>497.2547296470956</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>497.2547296470956</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>52.610933720000006</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.177178181170228</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1503.7587976543784</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>52.610933720000006</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1970.2645204787032</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$188,A5,'Species'!$U$2:$U$188))</x:f>
-        <x:v>103657.45609777265</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.177178181170228</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1503.7587976543784</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>79114.1544342614</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>24543.301663511244</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.310226429632198</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.31022642963219804</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>99.6626344987</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.405345824613947</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2542.996864034022</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>99.6626344987</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2559.0513332791697</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$188,A6,'Species'!$U$2:$U$188))</x:f>
-        <x:v>255041.79769201283</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.405345824613947</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2542.996864034022</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>253441.76699156305</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1600.0307004497736</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0063132084322275</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.006313208432227502</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6792.2532966034005</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.392367517195952</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2468.1270806591465</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6792.2532966034005</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2507.6645715580917</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$188,A7,'Species'!$U$2:$U$188))</x:f>
-        <x:v>17032692.952941</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.392367517195952</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2468.1270806591465</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>16764144.300043214</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>268548.65289778635</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0160192281867375</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01601922818673746</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4.6809852545</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.840706237558817</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>692.9569223717756</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4.6809852545</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>693.2777069098809</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$188,A8,'Species'!$U$2:$U$188))</x:f>
-        <x:v>3245.2227233187255</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.840706237558817</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>692.9569223717756</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3243.721135625983</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1.501587692742305</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.000462921327068</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0004629213270679399</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>102.12997982550002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.251065634023056</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1782.6481550048372</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>102.12997982550002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2098.2881636437537</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$188,A9,'Species'!$U$2:$U$188))</x:f>
-        <x:v>214298.12782102203</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.251065634023056</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1782.6481550048372</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>182061.82010660885</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>32236.307714413182</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1770624269027783</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.17706242690277818</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>3315.836306511</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.392654543184523</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2469.75880934383</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>3315.836306511</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2504.6060606039687</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$188,A10,'Species'!$U$2:$U$188))</x:f>
-        <x:v>8304863.70925813</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.392654543184523</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2469.75880934383</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>8189315.92834765</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>115547.78091047984</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.014109576663236</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.014109576663235875</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>187.848002503</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.1742197224565665</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>149.35498496204085</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>187.848002503</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>178.8050078988088</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$188,A11,'Species'!$U$2:$U$188))</x:f>
-        <x:v>33588.163571324374</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.1742197224565665</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>149.35498496204085</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>28056.035588984978</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>5532.127982339396</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1971813859728404</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.1971813859728405</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>572.8980161049</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.3650801480796946</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>231.78223594567393</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>572.8980161049</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>250.2243296387252</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$188,A12,'Species'!$U$2:$U$188))</x:f>
-        <x:v>143353.0220312042</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.3650801480796946</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>231.78223594567393</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>132787.58314163442</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>10565.438889569778</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0795664672825653</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.07956646728256532</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.6315792985</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.6315792985</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$188,A13,'Species'!$U$2:$U$188))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>759.325328227165</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>759.325328227165</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>687.6348662165</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.0675424363146537</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>116.82678795070507</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>687.6348662165</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>476.01790326761426</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$188,A14,'Species'!$U$2:$U$188))</x:f>
-        <x:v>327326.50723008474</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.0675424363146537</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>116.82678795070507</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>80334.17270298649</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>246992.33452709825</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>4.074561251041752</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>3.0745612510417515</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>994.5947985920999</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.577318507872074</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>377.8492007185556</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>994.5947985920999</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>531.373456233534</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$188,A15,'Species'!$U$2:$U$188))</x:f>
-        <x:v>528501.2756797797</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.577318507872074</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>377.8492007185556</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>375806.8496868577</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>152694.42599292198</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.4063109177497832</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.4063109177497832</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>330.8605102835999</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.5807663708216797</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>380.86088375758527</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>330.8605102835999</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>537.3941920313421</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$188,A16,'Species'!$U$2:$U$188))</x:f>
-        <x:v>177802.5165989327</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.5807663708216797</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>380.86088375758527</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>126011.82634709749</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>51790.690251835214</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.4109986479299064</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.4109986479299063</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>173.73788603329996</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.4208476475329386</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>263.5406711059763</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>173.73788603329996</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>291.8483387502596</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$188,A17,'Species'!$U$2:$U$188))</x:f>
-        <x:v>50705.113416800516</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.4208476475329386</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>263.5406711059763</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>45786.9990817495</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>4918.114335051017</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.1074128995933992</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.10741289959339914</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>21.371671899800003</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0841970860751813</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>12.139396203379674</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>21.371671899800003</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>12.181629803291878</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$188,A18,'Species'!$U$2:$U$188))</x:f>
-        <x:v>260.34179536077926</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0841970860751813</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>12.139396203379674</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>259.4391927203082</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0.9026026404710592</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0034790527637978</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0034790527637978035</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>214.8786995841</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.256517840200117</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>180.51688893810763</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>214.8786995841</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>188.8485977351661</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$188,A19,'Species'!$U$2:$U$188))</x:f>
-        <x:v>40579.5410996133</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.256517840200117</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>180.51688893810763</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>38789.23434798797</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>1790.3067516253286</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.046154732923162</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.04615473292316205</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>265.43101831229995</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.6380215395487427</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>434.53177495482555</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>265.43101831229995</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>435.22253503084863</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$188,A20,'Species'!$U$2:$U$188))</x:f>
-        <x:v>115521.5606656988</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.6380215395487427</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>434.53177495482555</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>115338.2115153105</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>183.34915038829786</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.001589665280738</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.001589665280737939</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>239.35258889129997</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.7669668388599313</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>584.7454334147221</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>239.35258889129997</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>913.1715490742682</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$188,A21,'Species'!$U$2:$U$188))</x:f>
-        <x:v>218569.9743728049</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.7669668388599313</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>584.7454334147221</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>139960.333330179</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>78609.64104262588</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.5616565720601612</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.5616565720601613</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>557.4469642864</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.10427186505417</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>127.13697239684443</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>557.4469642864</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>129.89200023859846</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$188,A22,'Species'!$U$2:$U$188))</x:f>
-        <x:v>72407.90121809505</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.10427186505417</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>127.13697239684443</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>70872.11931118475</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1535.7819069102989</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0216697612804126</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.021669761280412675</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>20.668221058100002</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.3485278201638415</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>223.11451262560135</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>20.668221058100002</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>243.48530967260734</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$188,A23,'Species'!$U$2:$U$188))</x:f>
-        <x:v>5032.408204713383</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.3485278201638415</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>223.11451262560135</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>4611.380068216173</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>421.02813649721065</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0913019812439961</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.09130198124399615</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>26.5973268938</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.656202404613881</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>453.1087037566054</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>26.5973268938</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>487.3550725798434</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$188,A24,'Species'!$U$2:$U$188))</x:f>
-        <x:v>12962.342178757719</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.656202404613881</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>453.1087037566054</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>12051.480312240417</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>910.8618665173017</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0755809114663002</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.0755809114663001</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>194.7836999241</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.807363056079173</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>641.74583107646</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>194.7836999241</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>642.9165025536587</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$188,A25,'Species'!$U$2:$U$188))</x:f>
-        <x:v>125229.65510966373</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.807363056079173</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>641.74583107646</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>125001.62738793937</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>228.02772172435652</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0018241980243718</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.001824198024371941</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>61.744968211499994</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.920228405591622</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>832.2013301098161</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>61.744968211499994</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>887.0592581277333</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$188,A26,'Species'!$U$2:$U$188))</x:f>
-        <x:v>54771.44569481366</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.920228405591622</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>832.2013301098161</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>51384.24467319861</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>3387.2010216150447</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.065919058325319</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.06591905832531907</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0de1f01592be4886"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R354cd5b5feae4d94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15576,7 +14127,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -15675,7 +14226,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>28287148.88364155</x:v>
+        <x:v>26410037.30568266</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15689,7 +14240,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>28287148.883641552</x:v>
+        <x:v>27236813.42580577</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15703,7 +14254,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1877111.5779588893</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15717,7 +14268,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-1050335.4578357786</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15728,9 +14279,9 @@
         <x:v>EEZ_903</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -15742,47 +14293,19 @@
         <x:v>EEZ_903</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_903</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_903</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9c374dadda0486f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4e52c894a154b8a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15829,7 +14352,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
